--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,382 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124018183</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56943</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gränsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>693658</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6662730</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124018181</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56703</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gränsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>693658</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6662730</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124018184</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gränsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>693658</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6662730</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124018183</v>
+        <v>124018184</v>
       </c>
       <c r="B3" t="n">
-        <v>56943</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,20 +814,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1054,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124018184</v>
+        <v>124018183</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>56943</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124018184</v>
+        <v>124018183</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>56943</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,20 +814,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124018181</v>
+        <v>124018184</v>
       </c>
       <c r="B4" t="n">
-        <v>56703</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,20 +938,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,11 +965,7 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1054,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124018183</v>
+        <v>124018181</v>
       </c>
       <c r="B5" t="n">
-        <v>56943</v>
+        <v>56703</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1093,7 +1089,11 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124018183</v>
+        <v>124018184</v>
       </c>
       <c r="B3" t="n">
-        <v>56943</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,20 +814,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124018184</v>
+        <v>124018183</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>56943</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,20 +938,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124018184</v>
+        <v>124018183</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,20 +814,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124018181</v>
+        <v>124018184</v>
       </c>
       <c r="B4" t="n">
-        <v>56725</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,20 +938,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,11 +965,7 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1054,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124018183</v>
+        <v>124018181</v>
       </c>
       <c r="B5" t="n">
-        <v>56965</v>
+        <v>56725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1093,7 +1089,11 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124018183</v>
+        <v>124018181</v>
       </c>
       <c r="B3" t="n">
-        <v>56965</v>
+        <v>56725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,7 +841,11 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1050,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124018181</v>
+        <v>124018183</v>
       </c>
       <c r="B5" t="n">
-        <v>56725</v>
+        <v>56965</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,16 +1070,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1089,11 +1093,7 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124018181</v>
+        <v>124018183</v>
       </c>
       <c r="B3" t="n">
-        <v>56725</v>
+        <v>56965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,11 +841,7 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1054,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124018183</v>
+        <v>124018181</v>
       </c>
       <c r="B5" t="n">
-        <v>56965</v>
+        <v>56725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,16 +1066,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1093,7 +1089,11 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124018183</v>
+        <v>124018181</v>
       </c>
       <c r="B3" t="n">
-        <v>56965</v>
+        <v>56725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,7 +841,11 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -926,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124018184</v>
+        <v>124018183</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56965</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,20 +942,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1050,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124018181</v>
+        <v>124018184</v>
       </c>
       <c r="B5" t="n">
-        <v>56725</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,20 +1066,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1089,11 +1093,7 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -930,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124018183</v>
+        <v>124018184</v>
       </c>
       <c r="B4" t="n">
-        <v>56965</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,20 +942,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1054,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124018184</v>
+        <v>124018183</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56965</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -930,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124018184</v>
+        <v>124018183</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56965</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,20 +942,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1054,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124018183</v>
+        <v>124018184</v>
       </c>
       <c r="B5" t="n">
-        <v>56965</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -675,62 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73954522</v>
+        <v>124018184</v>
       </c>
       <c r="B2" t="n">
-        <v>4964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101608</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kälkmossen S-ut, Upl</t>
+          <t>Gränsjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>693219.6666470609</v>
+        <v>693658</v>
       </c>
       <c r="R2" t="n">
-        <v>6662805.531064356</v>
+        <v>6662730</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-10-05</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-10-05</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>100-tals kläckhål</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,19 +776,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson, Jan-Olov Björklund</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -805,12 +797,7 @@
         <v>124018181</v>
       </c>
       <c r="B3" t="n">
-        <v>56725</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,16 +920,11 @@
         <v>124018183</v>
       </c>
       <c r="B4" t="n">
-        <v>56965</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1054,15 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124018184</v>
+        <v>69505988</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,49 +1047,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222133</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gränsjön, Upl</t>
+          <t>NV om Gränsjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693658</v>
+        <v>693482</v>
       </c>
       <c r="R5" t="n">
-        <v>6662730</v>
+        <v>6662766</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,22 +1101,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>06:51</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>06:51</t>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,18 +1123,27 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44709-2022 artfynd.xlsx
+++ b/artfynd/A 44709-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124018184</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124018181</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124018183</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,8 +1164,19 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69505988</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>